--- a/enrollment/019_preschool_summer_camp_enrollment_form--enrollment.xlsx
+++ b/enrollment/019_preschool_summer_camp_enrollment_form--enrollment.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -762,7 +762,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>form_title_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>form_description</t>
+          <t>form_description_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>form_category</t>
+          <t>form_category_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -923,12 +923,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>assigned_tool_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
+          <t>Assigned Tool 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -946,12 +946,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>form_category</t>
+          <t>form_category_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Form Category</t>
+          <t>Form Category 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -969,12 +969,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>form_title_3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Form Title</t>
+          <t>Form Title 3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -992,12 +992,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>form_description</t>
+          <t>form_description_3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Form Description</t>
+          <t>Form Description 3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>form_version</t>
+          <t>form_version_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Form Version</t>
+          <t>Form Version 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>form_category</t>
+          <t>form_category_4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Form Category</t>
+          <t>Form Category 4</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>form_id_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Form ID</t>
+          <t>Form Id 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1084,12 +1084,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>output_file</t>
+          <t>output_file_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Output File</t>
+          <t>Output File 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
